--- a/docs/M04_vs_M01_배틀시나리오.xlsx
+++ b/docs/M04_vs_M01_배틀시나리오.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ai\BattleAgent\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_BF8A336A46AFC5B09D40238E3C6D0B98BC836584" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294988D1-378E-46A8-957E-F55702360271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-45" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,20 @@
     <sheet name="SP 타이밍" sheetId="5" r:id="rId5"/>
     <sheet name="콤보 발동 기록" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
